--- a/samples/calibration01/stereo_calib3.xlsx
+++ b/samples/calibration01/stereo_calib3.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
